--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260624.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260624.xlsx
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>885,744,000</t>
+          <t>168,841,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.25%</t>
+          <t>10.16%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>168,841,000</t>
+          <t>885,744,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.06%</t>
+          <t>10.01%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.80%</t>
+          <t>6.67%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.01%</t>
+          <t>5.31%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>37,285,000</t>
+          <t>37,585,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.68%</t>
+          <t>4.69%</t>
         </is>
       </c>
     </row>
@@ -726,156 +726,156 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.61%</t>
+          <t>3.45%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>25,748,000</t>
+          <t>112,174,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.38%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>112,424,000</t>
+          <t>25,748,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.34%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>133,920,945</t>
+          <t>93,188,442</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>569,427,000</t>
+          <t>133,920,945</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.91%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>1,876</t>
+          <t>569,427,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.91%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>93,188,442</t>
+          <t>25,824,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>25,824,000</t>
+          <t>1,822</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.70%</t>
         </is>
       </c>
     </row>
@@ -924,73 +924,73 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>343,589,964</t>
+          <t>129,747,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>129,747,000</t>
+          <t>144,292,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>144,292,000</t>
+          <t>343,589,964</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>353,175,000</t>
+          <t>357,675,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
@@ -1144,51 +1144,51 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>51,217,000</t>
+          <t>269,366,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>269,366,000</t>
+          <t>51,517,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.87%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>7,583,657,966</t>
+          <t>6,436,933,244</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>11,307,680,134</t>
+          <t>10,922,023,061</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-1,112,563,814</t>
+          <t>-457,103,997</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
